--- a/Sequences/Clustering Tests.xlsx
+++ b/Sequences/Clustering Tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jordanbone/Documents/GitHub/IAV-Mach-Learning/Sequences/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EB7458D0-6664-D54F-8A09-67FA3E123A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDBED4C-26CF-A34A-AF7A-8D60192D4BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2800" yWindow="1640" windowWidth="27640" windowHeight="17500" xr2:uid="{6CBF63CA-BD3B-944C-BCF0-B6B471EBB7A8}"/>
+    <workbookView xWindow="1160" yWindow="500" windowWidth="27640" windowHeight="17500" xr2:uid="{6CBF63CA-BD3B-944C-BCF0-B6B471EBB7A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet4" sheetId="5" r:id="rId1"/>
@@ -285,7 +285,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,8 +322,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -515,11 +521,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -539,10 +554,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -552,7 +563,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -573,7 +584,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -588,6 +602,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -962,78 +980,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:38" ht="34" x14ac:dyDescent="0.4">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="C1" s="29"/>
+      <c r="U1" s="29" t="s">
         <v>37</v>
       </c>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
     </row>
     <row r="2" spans="2:38" x14ac:dyDescent="0.2">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="17" t="s">
+      <c r="D2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="V2" s="17" t="s">
+      <c r="V2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="W2" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="21"/>
-      <c r="AL2" s="17" t="s">
+      <c r="W2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="18"/>
+      <c r="AF2" s="19"/>
+      <c r="AG2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18"/>
+      <c r="AJ2" s="18"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="2:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
       <c r="D3" s="4">
         <v>75</v>
       </c>
@@ -1079,9 +1100,9 @@
       <c r="R3" s="4">
         <v>99</v>
       </c>
-      <c r="S3" s="25"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="18"/>
+      <c r="S3" s="16"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="24"/>
       <c r="W3" s="4">
         <v>75</v>
       </c>
@@ -1127,7 +1148,7 @@
       <c r="AK3" s="4">
         <v>99</v>
       </c>
-      <c r="AL3" s="18"/>
+      <c r="AL3" s="24"/>
     </row>
     <row r="4" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -1181,7 +1202,7 @@
       <c r="R4" s="8">
         <v>5177</v>
       </c>
-      <c r="S4" s="15">
+      <c r="S4" s="13">
         <v>15507</v>
       </c>
       <c r="U4" s="1" t="s">
@@ -1235,7 +1256,7 @@
       <c r="AK4" s="8">
         <v>4642</v>
       </c>
-      <c r="AL4" s="15">
+      <c r="AL4" s="13">
         <v>21880</v>
       </c>
     </row>
@@ -1261,19 +1282,19 @@
       <c r="H5" s="5">
         <v>5084</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="30">
         <v>18</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="30">
         <v>33</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="30">
         <v>56</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="30">
         <v>135</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="30">
         <v>5088</v>
       </c>
       <c r="N5" s="5">
@@ -1291,7 +1312,7 @@
       <c r="R5" s="6">
         <v>5089</v>
       </c>
-      <c r="S5" s="16"/>
+      <c r="S5" s="14"/>
       <c r="U5" s="12" t="s">
         <v>15</v>
       </c>
@@ -1313,19 +1334,19 @@
       <c r="AA5" s="5">
         <v>4600</v>
       </c>
-      <c r="AB5" s="5">
+      <c r="AB5" s="30">
         <v>18</v>
       </c>
-      <c r="AC5" s="5">
+      <c r="AC5" s="30">
         <v>28</v>
       </c>
-      <c r="AD5" s="5">
+      <c r="AD5" s="30">
         <v>54</v>
       </c>
-      <c r="AE5" s="5">
+      <c r="AE5" s="30">
         <v>2083</v>
       </c>
-      <c r="AF5" s="5">
+      <c r="AF5" s="30">
         <v>4600</v>
       </c>
       <c r="AG5" s="5">
@@ -1343,7 +1364,7 @@
       <c r="AK5" s="6">
         <v>4600</v>
       </c>
-      <c r="AL5" s="16"/>
+      <c r="AL5" s="14"/>
     </row>
     <row r="6" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
@@ -1397,7 +1418,7 @@
       <c r="R6" s="8">
         <v>2937</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="13">
         <v>15447</v>
       </c>
       <c r="U6" s="1" t="s">
@@ -1451,7 +1472,7 @@
       <c r="AK6" s="8">
         <v>4788</v>
       </c>
-      <c r="AL6" s="15">
+      <c r="AL6" s="13">
         <v>21829</v>
       </c>
     </row>
@@ -1477,19 +1498,19 @@
       <c r="H7" s="5">
         <v>2816</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="30">
         <v>27</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="30">
         <v>37</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="30">
         <v>41</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="30">
         <v>76</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="30">
         <v>2816</v>
       </c>
       <c r="N7" s="5">
@@ -1507,7 +1528,7 @@
       <c r="R7" s="6">
         <v>2816</v>
       </c>
-      <c r="S7" s="16"/>
+      <c r="S7" s="14"/>
       <c r="U7" s="12" t="s">
         <v>16</v>
       </c>
@@ -1529,19 +1550,19 @@
       <c r="AA7" s="5">
         <v>4746</v>
       </c>
-      <c r="AB7" s="5">
+      <c r="AB7" s="30">
         <v>58</v>
       </c>
-      <c r="AC7" s="5">
+      <c r="AC7" s="30">
         <v>124</v>
       </c>
-      <c r="AD7" s="5">
+      <c r="AD7" s="30">
         <v>152</v>
       </c>
-      <c r="AE7" s="5">
+      <c r="AE7" s="30">
         <v>3246</v>
       </c>
-      <c r="AF7" s="5">
+      <c r="AF7" s="30">
         <v>4750</v>
       </c>
       <c r="AG7" s="5">
@@ -1559,7 +1580,7 @@
       <c r="AK7" s="6">
         <v>4752</v>
       </c>
-      <c r="AL7" s="16"/>
+      <c r="AL7" s="14"/>
     </row>
     <row r="8" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -1613,7 +1634,7 @@
       <c r="R8" s="8">
         <v>5564</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="13">
         <v>15441</v>
       </c>
       <c r="U8" s="1" t="s">
@@ -1667,7 +1688,7 @@
       <c r="AK8" s="8">
         <v>8322</v>
       </c>
-      <c r="AL8" s="15">
+      <c r="AL8" s="13">
         <v>21856</v>
       </c>
     </row>
@@ -1693,19 +1714,19 @@
       <c r="H9" s="5">
         <v>5829</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="30">
         <v>11</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="30">
         <v>20</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="30">
         <v>29</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="30">
         <v>2402</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="30">
         <v>5840</v>
       </c>
       <c r="N9" s="5">
@@ -1723,7 +1744,7 @@
       <c r="R9" s="6">
         <v>5840</v>
       </c>
-      <c r="S9" s="16"/>
+      <c r="S9" s="14"/>
       <c r="U9" s="12" t="s">
         <v>14</v>
       </c>
@@ -1745,19 +1766,19 @@
       <c r="AA9" s="5">
         <v>8260</v>
       </c>
-      <c r="AB9" s="5">
+      <c r="AB9" s="30">
         <v>24</v>
       </c>
-      <c r="AC9" s="5">
+      <c r="AC9" s="30">
         <v>50</v>
       </c>
-      <c r="AD9" s="5">
+      <c r="AD9" s="30">
         <v>74</v>
       </c>
-      <c r="AE9" s="5">
+      <c r="AE9" s="30">
         <v>3512</v>
       </c>
-      <c r="AF9" s="5">
+      <c r="AF9" s="30">
         <v>8260</v>
       </c>
       <c r="AG9" s="5">
@@ -1775,7 +1796,7 @@
       <c r="AK9" s="6">
         <v>8260</v>
       </c>
-      <c r="AL9" s="16"/>
+      <c r="AL9" s="14"/>
     </row>
     <row r="10" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
@@ -1829,7 +1850,7 @@
       <c r="R10" s="8">
         <v>7058</v>
       </c>
-      <c r="S10" s="15">
+      <c r="S10" s="13">
         <v>15380</v>
       </c>
       <c r="U10" s="1" t="s">
@@ -1883,7 +1904,7 @@
       <c r="AK10" s="8">
         <v>6808</v>
       </c>
-      <c r="AL10" s="15">
+      <c r="AL10" s="13">
         <v>22106</v>
       </c>
     </row>
@@ -1909,19 +1930,19 @@
       <c r="H11" s="5">
         <v>7016</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="30">
         <v>31</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="30">
         <v>74</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="30">
         <v>500</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="30">
         <v>1942</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="30">
         <v>7016</v>
       </c>
       <c r="N11" s="5">
@@ -1939,7 +1960,7 @@
       <c r="R11" s="6">
         <v>7016</v>
       </c>
-      <c r="S11" s="16"/>
+      <c r="S11" s="14"/>
       <c r="U11" s="12" t="s">
         <v>13</v>
       </c>
@@ -1961,19 +1982,19 @@
       <c r="AA11" s="5">
         <v>6740</v>
       </c>
-      <c r="AB11" s="5">
+      <c r="AB11" s="30">
         <v>20</v>
       </c>
-      <c r="AC11" s="5">
+      <c r="AC11" s="30">
         <v>32</v>
       </c>
-      <c r="AD11" s="5">
+      <c r="AD11" s="30">
         <v>154</v>
       </c>
-      <c r="AE11" s="5">
+      <c r="AE11" s="30">
         <v>2038</v>
       </c>
-      <c r="AF11" s="5">
+      <c r="AF11" s="30">
         <v>6740</v>
       </c>
       <c r="AG11" s="5">
@@ -1991,7 +2012,7 @@
       <c r="AK11" s="6">
         <v>6740</v>
       </c>
-      <c r="AL11" s="16"/>
+      <c r="AL11" s="14"/>
     </row>
     <row r="12" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
@@ -2045,7 +2066,7 @@
       <c r="R12" s="8">
         <v>3225</v>
       </c>
-      <c r="S12" s="15">
+      <c r="S12" s="13">
         <v>14682</v>
       </c>
       <c r="U12" s="1" t="s">
@@ -2099,7 +2120,7 @@
       <c r="AK12" s="8">
         <v>2155</v>
       </c>
-      <c r="AL12" s="15">
+      <c r="AL12" s="13">
         <v>21865</v>
       </c>
     </row>
@@ -2125,19 +2146,19 @@
       <c r="H13" s="5">
         <v>3171</v>
       </c>
-      <c r="I13" s="5">
-        <v>5</v>
-      </c>
-      <c r="J13" s="5">
+      <c r="I13" s="30">
+        <v>5</v>
+      </c>
+      <c r="J13" s="30">
         <v>8</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="30">
         <v>12</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="30">
         <v>52</v>
       </c>
-      <c r="M13" s="5">
+      <c r="M13" s="30">
         <v>3171</v>
       </c>
       <c r="N13" s="5">
@@ -2155,7 +2176,7 @@
       <c r="R13" s="6">
         <v>3171</v>
       </c>
-      <c r="S13" s="16"/>
+      <c r="S13" s="14"/>
       <c r="U13" s="12" t="s">
         <v>17</v>
       </c>
@@ -2177,19 +2198,19 @@
       <c r="AA13" s="5">
         <v>2243</v>
       </c>
-      <c r="AB13" s="5">
+      <c r="AB13" s="30">
         <v>7</v>
       </c>
-      <c r="AC13" s="5">
+      <c r="AC13" s="30">
         <v>10</v>
       </c>
-      <c r="AD13" s="5">
+      <c r="AD13" s="30">
         <v>614</v>
       </c>
-      <c r="AE13" s="5">
+      <c r="AE13" s="30">
         <v>70</v>
       </c>
-      <c r="AF13" s="5">
+      <c r="AF13" s="30">
         <v>2244</v>
       </c>
       <c r="AG13" s="5">
@@ -2207,7 +2228,7 @@
       <c r="AK13" s="6">
         <v>2244</v>
       </c>
-      <c r="AL13" s="16"/>
+      <c r="AL13" s="14"/>
     </row>
     <row r="14" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -2261,7 +2282,7 @@
       <c r="R14" s="8">
         <v>2683</v>
       </c>
-      <c r="S14" s="15">
+      <c r="S14" s="13">
         <v>15442</v>
       </c>
       <c r="U14" s="1" t="s">
@@ -2315,7 +2336,7 @@
       <c r="AK14" s="8">
         <v>2263</v>
       </c>
-      <c r="AL14" s="15">
+      <c r="AL14" s="13">
         <v>21845</v>
       </c>
     </row>
@@ -2341,19 +2362,19 @@
       <c r="H15" s="5">
         <v>2421</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="30">
         <v>25</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="30">
         <v>36</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="30">
         <v>274</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="30">
         <v>544</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="30">
         <v>2422</v>
       </c>
       <c r="N15" s="5">
@@ -2371,7 +2392,7 @@
       <c r="R15" s="6">
         <v>2422</v>
       </c>
-      <c r="S15" s="16"/>
+      <c r="S15" s="14"/>
       <c r="U15" s="12" t="s">
         <v>18</v>
       </c>
@@ -2393,19 +2414,19 @@
       <c r="AA15" s="5">
         <v>2376</v>
       </c>
-      <c r="AB15" s="5">
+      <c r="AB15" s="30">
         <v>13</v>
       </c>
-      <c r="AC15" s="5">
+      <c r="AC15" s="30">
         <v>21</v>
       </c>
-      <c r="AD15" s="5">
+      <c r="AD15" s="30">
         <v>47</v>
       </c>
-      <c r="AE15" s="5">
+      <c r="AE15" s="30">
         <v>294</v>
       </c>
-      <c r="AF15" s="5">
+      <c r="AF15" s="30">
         <v>2377</v>
       </c>
       <c r="AG15" s="5">
@@ -2423,7 +2444,7 @@
       <c r="AK15" s="6">
         <v>2377</v>
       </c>
-      <c r="AL15" s="16"/>
+      <c r="AL15" s="14"/>
     </row>
     <row r="16" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -2477,7 +2498,7 @@
       <c r="R16" s="8">
         <v>542</v>
       </c>
-      <c r="S16" s="15">
+      <c r="S16" s="13">
         <v>15335</v>
       </c>
       <c r="U16" s="1" t="s">
@@ -2531,7 +2552,7 @@
       <c r="AK16" s="8">
         <v>1576</v>
       </c>
-      <c r="AL16" s="15">
+      <c r="AL16" s="13">
         <v>21791</v>
       </c>
     </row>
@@ -2557,19 +2578,19 @@
       <c r="H17" s="5">
         <v>569</v>
       </c>
-      <c r="I17" s="5">
-        <v>3</v>
-      </c>
-      <c r="J17" s="5">
-        <v>3</v>
-      </c>
-      <c r="K17" s="5">
-        <v>5</v>
-      </c>
-      <c r="L17" s="5">
+      <c r="I17" s="30">
+        <v>3</v>
+      </c>
+      <c r="J17" s="30">
+        <v>3</v>
+      </c>
+      <c r="K17" s="30">
+        <v>5</v>
+      </c>
+      <c r="L17" s="30">
         <v>33</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="30">
         <v>569</v>
       </c>
       <c r="N17" s="5">
@@ -2587,7 +2608,7 @@
       <c r="R17" s="6">
         <v>569</v>
       </c>
-      <c r="S17" s="16"/>
+      <c r="S17" s="14"/>
       <c r="U17" s="12" t="s">
         <v>19</v>
       </c>
@@ -2609,19 +2630,19 @@
       <c r="AA17" s="5">
         <v>1552</v>
       </c>
-      <c r="AB17" s="5">
-        <v>2</v>
-      </c>
-      <c r="AC17" s="5">
-        <v>4</v>
-      </c>
-      <c r="AD17" s="5">
-        <v>6</v>
-      </c>
-      <c r="AE17" s="5">
+      <c r="AB17" s="30">
+        <v>2</v>
+      </c>
+      <c r="AC17" s="30">
+        <v>4</v>
+      </c>
+      <c r="AD17" s="30">
+        <v>6</v>
+      </c>
+      <c r="AE17" s="30">
         <v>260</v>
       </c>
-      <c r="AF17" s="5">
+      <c r="AF17" s="30">
         <v>1552</v>
       </c>
       <c r="AG17" s="5">
@@ -2639,7 +2660,7 @@
       <c r="AK17" s="6">
         <v>1552</v>
       </c>
-      <c r="AL17" s="16"/>
+      <c r="AL17" s="14"/>
     </row>
     <row r="18" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
@@ -2693,7 +2714,7 @@
       <c r="R18" s="8">
         <v>2414</v>
       </c>
-      <c r="S18" s="15">
+      <c r="S18" s="13">
         <v>15124</v>
       </c>
       <c r="U18" s="1" t="s">
@@ -2747,7 +2768,7 @@
       <c r="AK18" s="8">
         <v>4234</v>
       </c>
-      <c r="AL18" s="15">
+      <c r="AL18" s="13">
         <v>21770</v>
       </c>
     </row>
@@ -2773,19 +2794,19 @@
       <c r="H19" s="5">
         <v>2366</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="30">
         <v>14</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="30">
         <v>58</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="30">
         <v>106</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="30">
         <v>555</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="30">
         <v>2366</v>
       </c>
       <c r="N19" s="5">
@@ -2803,7 +2824,7 @@
       <c r="R19" s="6">
         <v>2366</v>
       </c>
-      <c r="S19" s="16"/>
+      <c r="S19" s="14"/>
       <c r="U19" s="12" t="s">
         <v>20</v>
       </c>
@@ -2825,19 +2846,19 @@
       <c r="AA19" s="5">
         <v>4168</v>
       </c>
-      <c r="AB19" s="5">
+      <c r="AB19" s="30">
         <v>20</v>
       </c>
-      <c r="AC19" s="5">
+      <c r="AC19" s="30">
         <v>44</v>
       </c>
-      <c r="AD19" s="5">
+      <c r="AD19" s="30">
         <v>94</v>
       </c>
-      <c r="AE19" s="5">
+      <c r="AE19" s="30">
         <v>586</v>
       </c>
-      <c r="AF19" s="5">
+      <c r="AF19" s="30">
         <v>4168</v>
       </c>
       <c r="AG19" s="5">
@@ -2855,7 +2876,7 @@
       <c r="AK19" s="6">
         <v>4168</v>
       </c>
-      <c r="AL19" s="16"/>
+      <c r="AL19" s="14"/>
     </row>
     <row r="20" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
@@ -2909,7 +2930,7 @@
       <c r="R20" s="8">
         <v>1766</v>
       </c>
-      <c r="S20" s="15">
+      <c r="S20" s="13">
         <v>15228</v>
       </c>
       <c r="U20" s="1" t="s">
@@ -2963,7 +2984,7 @@
       <c r="AK20" s="8">
         <v>2740</v>
       </c>
-      <c r="AL20" s="15">
+      <c r="AL20" s="13">
         <v>21760</v>
       </c>
     </row>
@@ -2989,19 +3010,19 @@
       <c r="H21" s="5">
         <v>1735</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="30">
         <v>9</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="30">
         <v>29</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="30">
         <v>211</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="30">
         <v>437</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="30">
         <v>1735</v>
       </c>
       <c r="N21" s="5">
@@ -3019,7 +3040,7 @@
       <c r="R21" s="6">
         <v>1735</v>
       </c>
-      <c r="S21" s="16"/>
+      <c r="S21" s="14"/>
       <c r="U21" s="12" t="s">
         <v>22</v>
       </c>
@@ -3041,19 +3062,19 @@
       <c r="AA21" s="5">
         <v>2620</v>
       </c>
-      <c r="AB21" s="5">
-        <v>4</v>
-      </c>
-      <c r="AC21" s="5">
+      <c r="AB21" s="30">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="30">
         <v>34</v>
       </c>
-      <c r="AD21" s="5">
+      <c r="AD21" s="30">
         <v>60</v>
       </c>
-      <c r="AE21" s="5">
+      <c r="AE21" s="30">
         <v>462</v>
       </c>
-      <c r="AF21" s="5">
+      <c r="AF21" s="30">
         <v>2620</v>
       </c>
       <c r="AG21" s="5">
@@ -3071,7 +3092,7 @@
       <c r="AK21" s="6">
         <v>2620</v>
       </c>
-      <c r="AL21" s="16"/>
+      <c r="AL21" s="14"/>
     </row>
     <row r="22" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
@@ -3125,7 +3146,7 @@
       <c r="R22" s="8">
         <v>3189</v>
       </c>
-      <c r="S22" s="15">
+      <c r="S22" s="13">
         <v>15293</v>
       </c>
       <c r="U22" s="1" t="s">
@@ -3179,7 +3200,7 @@
       <c r="AK22" s="8">
         <v>7658</v>
       </c>
-      <c r="AL22" s="15">
+      <c r="AL22" s="13">
         <v>21737</v>
       </c>
     </row>
@@ -3205,19 +3226,19 @@
       <c r="H23" s="5">
         <v>3200</v>
       </c>
-      <c r="I23" s="5">
-        <v>4</v>
-      </c>
-      <c r="J23" s="5">
+      <c r="I23" s="30">
+        <v>4</v>
+      </c>
+      <c r="J23" s="30">
         <v>116</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="30">
         <v>81</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="30">
         <v>554</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23" s="30">
         <v>3200</v>
       </c>
       <c r="N23" s="5">
@@ -3235,7 +3256,7 @@
       <c r="R23" s="6">
         <v>3200</v>
       </c>
-      <c r="S23" s="16"/>
+      <c r="S23" s="14"/>
       <c r="U23" s="12" t="s">
         <v>21</v>
       </c>
@@ -3257,19 +3278,19 @@
       <c r="AA23" s="5">
         <v>7650</v>
       </c>
-      <c r="AB23" s="5">
+      <c r="AB23" s="30">
         <v>10</v>
       </c>
-      <c r="AC23" s="5">
+      <c r="AC23" s="30">
         <v>70</v>
       </c>
-      <c r="AD23" s="5">
+      <c r="AD23" s="30">
         <v>264</v>
       </c>
-      <c r="AE23" s="5">
+      <c r="AE23" s="30">
         <v>1034</v>
       </c>
-      <c r="AF23" s="5">
+      <c r="AF23" s="30">
         <v>7650</v>
       </c>
       <c r="AG23" s="5">
@@ -3287,42 +3308,42 @@
       <c r="AK23" s="6">
         <v>7650</v>
       </c>
-      <c r="AL23" s="16"/>
+      <c r="AL23" s="14"/>
     </row>
     <row r="27" spans="2:38" x14ac:dyDescent="0.2">
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="24"/>
-      <c r="P27" s="24"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
     </row>
     <row r="28" spans="2:38" x14ac:dyDescent="0.2">
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="22"/>
+      <c r="D28" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="20"/>
     </row>
     <row r="29" spans="2:38" x14ac:dyDescent="0.2">
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
       <c r="D29" s="10">
         <v>75</v>
       </c>
@@ -3376,27 +3397,15 @@
       <sortCondition ref="B2:B23"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="36">
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="S10:S11"/>
-    <mergeCell ref="S12:S13"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B27:P27"/>
+  <mergeCells count="38">
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="AL10:AL11"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AL6:AL7"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="V2:V3"/>
     <mergeCell ref="AL22:AL23"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="AB2:AF2"/>
@@ -3407,12 +3416,26 @@
     <mergeCell ref="AL18:AL19"/>
     <mergeCell ref="AL20:AL21"/>
     <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="AL10:AL11"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AL6:AL7"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B27:P27"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="S10:S11"/>
+    <mergeCell ref="S12:S13"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:R2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
@@ -3433,30 +3456,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="28" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="27" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="2">
         <v>75</v>
       </c>
@@ -3472,7 +3495,7 @@
       <c r="H2" s="2">
         <v>99</v>
       </c>
-      <c r="I2" s="29"/>
+      <c r="I2" s="28"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -3499,7 +3522,7 @@
       <c r="H3" s="3">
         <v>34149</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="26">
         <v>152879</v>
       </c>
     </row>
@@ -3528,7 +3551,7 @@
       <c r="H4" s="3">
         <v>34435</v>
       </c>
-      <c r="I4" s="27"/>
+      <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
@@ -3555,7 +3578,7 @@
       <c r="H5" s="3">
         <v>34555</v>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -3582,7 +3605,7 @@
       <c r="H6" s="3">
         <v>34207</v>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -3609,7 +3632,7 @@
       <c r="H7" s="3">
         <v>34223</v>
       </c>
-      <c r="I7" s="27"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
@@ -3636,7 +3659,7 @@
       <c r="H8" s="3">
         <v>34224</v>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -3663,7 +3686,7 @@
       <c r="H9" s="1">
         <v>45061</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="25">
         <v>218439</v>
       </c>
     </row>
@@ -3692,7 +3715,7 @@
       <c r="H10" s="1">
         <v>45236</v>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
@@ -3719,7 +3742,7 @@
       <c r="H11" s="1">
         <v>45186</v>
       </c>
-      <c r="I11" s="26"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -3746,7 +3769,7 @@
       <c r="H12" s="1">
         <v>44955</v>
       </c>
-      <c r="I12" s="26"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
@@ -3773,7 +3796,7 @@
       <c r="H13" s="1">
         <v>44961</v>
       </c>
-      <c r="I13" s="26"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -3800,7 +3823,7 @@
       <c r="H14" s="1">
         <v>44963</v>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="7">
